--- a/Config/HeroEffectsConfig.xlsx
+++ b/Config/HeroEffectsConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="8190" windowHeight="9975"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Type</t>
   </si>
   <si>
+    <t>IsProjectile</t>
+  </si>
+  <si>
     <t>Effects</t>
   </si>
   <si>
@@ -65,6 +68,9 @@
   </si>
   <si>
     <t>特效类型</t>
+  </si>
+  <si>
+    <t>是否投射物</t>
   </si>
   <si>
     <t>资源名字</t>
@@ -704,7 +710,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -717,9 +723,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1069,19 +1072,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="3.075" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.5333333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.1916666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.15" style="1" customWidth="1"/>
-    <col min="6" max="16375" width="9" style="1" customWidth="1"/>
-    <col min="16376" max="16384" width="9" style="1"/>
+    <col min="4" max="5" width="10.1916666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.15" style="1" customWidth="1"/>
+    <col min="7" max="16376" width="9" style="1" customWidth="1"/>
+    <col min="16377" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1097,72 +1100,83 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="5">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="C6"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="3"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:6">
       <c r="C13" s="1"/>
     </row>
   </sheetData>

--- a/Config/HeroEffectsConfig.xlsx
+++ b/Config/HeroEffectsConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cardclient\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\cardclient\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -46,6 +46,9 @@
     <t>IsProjectile</t>
   </si>
   <si>
+    <t>rolepoint</t>
+  </si>
+  <si>
     <t>Effects</t>
   </si>
   <si>
@@ -71,6 +74,9 @@
   </si>
   <si>
     <t>是否投射物</t>
+  </si>
+  <si>
+    <t>人物位置点</t>
   </si>
   <si>
     <t>资源名字</t>
@@ -1072,19 +1078,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="3.075" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.5333333333333" style="2" customWidth="1"/>
-    <col min="4" max="5" width="10.1916666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.15" style="1" customWidth="1"/>
-    <col min="7" max="16376" width="9" style="1" customWidth="1"/>
-    <col min="16377" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="13.75" style="1" customWidth="1"/>
+    <col min="5" max="6" width="20.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.15" style="1" customWidth="1"/>
+    <col min="8" max="16377" width="9" style="1" customWidth="1"/>
+    <col min="16378" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1103,80 +1110,97 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="3">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="C6"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="3"/>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="3"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="C13" s="1"/>
     </row>
   </sheetData>

--- a/Config/HeroEffectsConfig.xlsx
+++ b/Config/HeroEffectsConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\cardclient\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cardclient\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11655"/>
+    <workbookView windowWidth="14265" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -716,7 +716,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -727,8 +727,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1083,9 +1086,10 @@
   <cols>
     <col min="1" max="1" width="3.075" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5333333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.75" style="1" customWidth="1"/>
-    <col min="5" max="6" width="20.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.15" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.9" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.3583333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.15" style="1" customWidth="1"/>
     <col min="8" max="16377" width="9" style="1" customWidth="1"/>
     <col min="16378" max="16384" width="9" style="1"/>
@@ -1171,7 +1175,7 @@
       <c r="D5" s="4">
         <v>0</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1192,13 +1196,15 @@
         <v>21</v>
       </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
       <c r="C13" s="1"/>

--- a/Config/HeroEffectsConfig.xlsx
+++ b/Config/HeroEffectsConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14265" windowHeight="10605"/>
+    <workbookView windowWidth="15345" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -94,6 +94,30 @@
     <t>HeroAttackArrow01</t>
   </si>
   <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Aoshufeidan01</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>Aoshufeidan02</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>Aoshufeidan03</t>
+  </si>
+  <si>
+    <t>0.4</t>
+  </si>
+  <si>
     <t>201</t>
   </si>
   <si>
@@ -101,6 +125,12 @@
   </si>
   <si>
     <t>HeroAttackFenlie01</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Aoshufeidan04</t>
   </si>
 </sst>
 </file>
@@ -716,7 +746,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -732,6 +762,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1081,7 +1114,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="3.075" style="1" customWidth="1"/>
@@ -1186,28 +1219,108 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="C6"/>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5">
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="C9"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="C10"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="C11"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5">
         <v>0</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="3">
+      <c r="F12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="3">
         <v>0.4</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="C13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/HeroEffectsConfig.xlsx
+++ b/Config/HeroEffectsConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15345" windowHeight="10605"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="66">
   <si>
     <t>##var</t>
   </si>
@@ -118,6 +118,75 @@
     <t>0.4</t>
   </si>
   <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>KuangZhanShi01</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>KuangZhanShi02</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>KuangZhanShi03</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>KuangZhanShi04</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>KuangZhanShi05</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>HeroAttackTianliu01</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>HeroAttackTianliu02</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>HeroAttackHuoqiu01</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>SaManJiSiAttack01</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>WuSengAttack01</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>ShengQiShiAttack01</t>
+  </si>
+  <si>
     <t>201</t>
   </si>
   <si>
@@ -131,6 +200,36 @@
   </si>
   <si>
     <t>Aoshufeidan04</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>KuangZhanShi06</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>HeroAttackHuoqiu02</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>SaManJiSiAttack02</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>ShengQiShiAttack02</t>
   </si>
 </sst>
 </file>
@@ -746,7 +845,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -754,12 +853,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1114,7 +1207,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="3.075" style="1" customWidth="1"/>
@@ -1205,13 +1298,13 @@
       <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>0</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="3">
         <v>0</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="3">
@@ -1228,7 +1321,7 @@
       <c r="E6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G6" s="3">
@@ -1248,7 +1341,7 @@
       <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G7" s="3">
@@ -1268,7 +1361,7 @@
       <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1276,51 +1369,306 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="C9"/>
+      <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="C10"/>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="C11"/>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
       <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0.4</v>
+        <v>35</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="B13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="5">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="C20"/>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="C21"/>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="3">
+      <c r="F22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="3">
         <v>0.45</v>
       </c>
     </row>
-    <row r="18" spans="3:3">
-      <c r="C18" s="1"/>
+    <row r="24" spans="2:7">
+      <c r="B24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
+      <c r="B25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="B26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="C28" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/HeroEffectsConfig.xlsx
+++ b/Config/HeroEffectsConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="82">
   <si>
     <t>##var</t>
   </si>
@@ -152,6 +152,9 @@
   </si>
   <si>
     <t>110</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>HeroAttackTianliu01</t>
@@ -1511,8 +1514,11 @@
       <c r="C14" t="s">
         <v>22</v>
       </c>
+      <c r="F14" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="G14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>27</v>
@@ -1520,10 +1526,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>33</v>
@@ -1532,7 +1538,7 @@
         <v>33</v>
       </c>
       <c r="G15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>27</v>
@@ -1540,7 +1546,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
@@ -1552,10 +1558,10 @@
         <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>31</v>
@@ -1563,7 +1569,7 @@
     </row>
     <row r="17" spans="2:9">
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -1575,27 +1581,27 @@
         <v>27</v>
       </c>
       <c r="G17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I18">
         <v>0.5</v>
@@ -1603,24 +1609,24 @@
     </row>
     <row r="19" spans="2:9">
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
       </c>
       <c r="G19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="2:9">
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
@@ -1629,13 +1635,13 @@
         <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="2:9">
@@ -1643,10 +1649,10 @@
     </row>
     <row r="22" spans="2:9">
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -1654,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H22" s="3">
         <v>0.7</v>
@@ -1662,16 +1668,16 @@
     </row>
     <row r="23" spans="2:9">
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H23" s="3">
         <v>0.45</v>
@@ -1679,16 +1685,16 @@
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H24" s="3">
         <v>0.4</v>
@@ -1696,16 +1702,16 @@
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H25" s="3">
         <v>0.4</v>
@@ -1713,64 +1719,64 @@
     </row>
     <row r="26" spans="2:9">
       <c r="B26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="2:9">
       <c r="B28" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="2:9">
       <c r="B29" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>27</v>
@@ -1778,13 +1784,13 @@
     </row>
     <row r="30" spans="2:9">
       <c r="B30" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>27</v>
